--- a/data/raw/sales/Week 33/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 33/Tonor/Vendor Sales (SP-API).xlsx
@@ -298,7 +298,7 @@
     <t>2026-08-09</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>2026-08-15</t>
   </si>
 </sst>
 </file>
@@ -729,13 +729,13 @@
         <v>78</v>
       </c>
       <c r="H2">
+        <v>55</v>
+      </c>
+      <c r="I2">
+        <v>74529.39999999999</v>
+      </c>
+      <c r="J2">
         <v>42</v>
-      </c>
-      <c r="I2">
-        <v>56913.36</v>
-      </c>
-      <c r="J2">
-        <v>34</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>79</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2075.42</v>
+        <v>4150.84</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -823,10 +823,10 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>23011.01</v>
+        <v>25083.04</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="s">
         <v>92</v>
@@ -876,7 +876,7 @@
         <v>9605.08</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -964,13 +964,13 @@
         <v>81</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>21132.24</v>
+        <v>22893.26</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>19233.92</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>86</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>4506.78</v>
+        <v>9013.549999999999</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1340,10 +1340,10 @@
         <v>88</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>1948.31</v>
+        <v>3896.62</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1387,10 +1387,10 @@
         <v>88</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16">
-        <v>15205.92</v>
+        <v>18587.28</v>
       </c>
       <c r="J16">
         <v>11</v>
@@ -1434,13 +1434,13 @@
         <v>89</v>
       </c>
       <c r="H17">
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <v>20921.22</v>
+      </c>
+      <c r="J17">
         <v>8</v>
-      </c>
-      <c r="I17">
-        <v>18596.64</v>
-      </c>
-      <c r="J17">
-        <v>7</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1481,10 +1481,10 @@
         <v>90</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18">
-        <v>16976.28</v>
+        <v>18670.35</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" t="s">
         <v>92</v>
@@ -1528,13 +1528,13 @@
         <v>91</v>
       </c>
       <c r="H19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I19">
-        <v>24393.28</v>
+        <v>30491.6</v>
       </c>
       <c r="J19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19">
         <v>0</v>
